--- a/artfynd/A 48338-2021 artfynd.xlsx
+++ b/artfynd/A 48338-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121066949</v>
+        <v>121066948</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607549</v>
+        <v>607538</v>
       </c>
       <c r="R2" t="n">
-        <v>7222874</v>
+        <v>7222859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121066946</v>
+        <v>121066941</v>
       </c>
       <c r="B3" t="n">
-        <v>78680</v>
+        <v>79710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607439</v>
+        <v>607301</v>
       </c>
       <c r="R3" t="n">
-        <v>7222815</v>
+        <v>7222757</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066948</v>
+        <v>121066938</v>
       </c>
       <c r="B4" t="n">
-        <v>78680</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607538</v>
+        <v>607194</v>
       </c>
       <c r="R4" t="n">
-        <v>7222859</v>
+        <v>7222802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066952</v>
+        <v>121066945</v>
       </c>
       <c r="B5" t="n">
-        <v>82382</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607715</v>
+        <v>607423</v>
       </c>
       <c r="R5" t="n">
-        <v>7222908</v>
+        <v>7222823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066942</v>
+        <v>121066951</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607311</v>
+        <v>607676</v>
       </c>
       <c r="R6" t="n">
-        <v>7222763</v>
+        <v>7222895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066950</v>
+        <v>121066953</v>
       </c>
       <c r="B7" t="n">
-        <v>97025</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607623</v>
+        <v>607733</v>
       </c>
       <c r="R7" t="n">
-        <v>7222896</v>
+        <v>7222910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066940</v>
+        <v>121066954</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>79710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607187</v>
+        <v>607755</v>
       </c>
       <c r="R8" t="n">
-        <v>7222814</v>
+        <v>7222905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121066951</v>
+        <v>121066947</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607676</v>
+        <v>607445</v>
       </c>
       <c r="R9" t="n">
-        <v>7222895</v>
+        <v>7222822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121066938</v>
+        <v>121066937</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>97998</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607194</v>
+        <v>607199</v>
       </c>
       <c r="R10" t="n">
-        <v>7222802</v>
+        <v>7222792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121066941</v>
+        <v>121066940</v>
       </c>
       <c r="B11" t="n">
-        <v>79707</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607301</v>
+        <v>607187</v>
       </c>
       <c r="R11" t="n">
-        <v>7222757</v>
+        <v>7222814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121066945</v>
+        <v>121066943</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>98102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607423</v>
+        <v>607316</v>
       </c>
       <c r="R12" t="n">
-        <v>7222823</v>
+        <v>7222787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066939</v>
+        <v>121066950</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>97035</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607185</v>
+        <v>607623</v>
       </c>
       <c r="R13" t="n">
-        <v>7222801</v>
+        <v>7222896</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066953</v>
+        <v>121066944</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607733</v>
+        <v>607423</v>
       </c>
       <c r="R14" t="n">
-        <v>7222910</v>
+        <v>7222826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121066954</v>
+        <v>121066946</v>
       </c>
       <c r="B15" t="n">
-        <v>79707</v>
+        <v>78683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607755</v>
+        <v>607439</v>
       </c>
       <c r="R15" t="n">
-        <v>7222905</v>
+        <v>7222815</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066943</v>
+        <v>121066949</v>
       </c>
       <c r="B16" t="n">
-        <v>98092</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607316</v>
+        <v>607549</v>
       </c>
       <c r="R16" t="n">
-        <v>7222787</v>
+        <v>7222874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121066934</v>
+        <v>121066952</v>
       </c>
       <c r="B17" t="n">
-        <v>77530</v>
+        <v>82385</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607175</v>
+        <v>607715</v>
       </c>
       <c r="R17" t="n">
-        <v>7222788</v>
+        <v>7222908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066944</v>
+        <v>121066934</v>
       </c>
       <c r="B18" t="n">
-        <v>79680</v>
+        <v>77533</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607423</v>
+        <v>607175</v>
       </c>
       <c r="R18" t="n">
-        <v>7222826</v>
+        <v>7222788</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121066955</v>
+        <v>121066942</v>
       </c>
       <c r="B19" t="n">
-        <v>82382</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607758</v>
+        <v>607311</v>
       </c>
       <c r="R19" t="n">
-        <v>7222909</v>
+        <v>7222763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121066937</v>
+        <v>121066955</v>
       </c>
       <c r="B20" t="n">
-        <v>97988</v>
+        <v>82385</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607199</v>
+        <v>607758</v>
       </c>
       <c r="R20" t="n">
-        <v>7222792</v>
+        <v>7222909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121066947</v>
+        <v>121066939</v>
       </c>
       <c r="B21" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607445</v>
+        <v>607185</v>
       </c>
       <c r="R21" t="n">
-        <v>7222822</v>
+        <v>7222801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 48338-2021 artfynd.xlsx
+++ b/artfynd/A 48338-2021 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066938</v>
+        <v>121066945</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607194</v>
+        <v>607423</v>
       </c>
       <c r="R4" t="n">
-        <v>7222802</v>
+        <v>7222823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066945</v>
+        <v>121066951</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607423</v>
+        <v>607676</v>
       </c>
       <c r="R5" t="n">
-        <v>7222823</v>
+        <v>7222895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066951</v>
+        <v>121066938</v>
       </c>
       <c r="B6" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607676</v>
+        <v>607194</v>
       </c>
       <c r="R6" t="n">
-        <v>7222895</v>
+        <v>7222802</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48338-2021 artfynd.xlsx
+++ b/artfynd/A 48338-2021 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066945</v>
+        <v>121066938</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607423</v>
+        <v>607194</v>
       </c>
       <c r="R4" t="n">
-        <v>7222823</v>
+        <v>7222802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066951</v>
+        <v>121066945</v>
       </c>
       <c r="B5" t="n">
-        <v>79711</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607676</v>
+        <v>607423</v>
       </c>
       <c r="R5" t="n">
-        <v>7222895</v>
+        <v>7222823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066938</v>
+        <v>121066951</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607194</v>
+        <v>607676</v>
       </c>
       <c r="R6" t="n">
-        <v>7222802</v>
+        <v>7222895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48338-2021 artfynd.xlsx
+++ b/artfynd/A 48338-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121066948</v>
+        <v>121066939</v>
       </c>
       <c r="B2" t="n">
-        <v>78683</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607538</v>
+        <v>607185</v>
       </c>
       <c r="R2" t="n">
-        <v>7222859</v>
+        <v>7222801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121066941</v>
+        <v>121066945</v>
       </c>
       <c r="B3" t="n">
-        <v>79710</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607301</v>
+        <v>607423</v>
       </c>
       <c r="R3" t="n">
-        <v>7222757</v>
+        <v>7222823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066938</v>
+        <v>121066955</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607194</v>
+        <v>607758</v>
       </c>
       <c r="R4" t="n">
-        <v>7222802</v>
+        <v>7222909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066945</v>
+        <v>121066952</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>82385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607423</v>
+        <v>607715</v>
       </c>
       <c r="R5" t="n">
-        <v>7222823</v>
+        <v>7222908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066953</v>
+        <v>121066944</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607733</v>
+        <v>607423</v>
       </c>
       <c r="R7" t="n">
-        <v>7222910</v>
+        <v>7222826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066954</v>
+        <v>121066948</v>
       </c>
       <c r="B8" t="n">
-        <v>79710</v>
+        <v>78683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607755</v>
+        <v>607538</v>
       </c>
       <c r="R8" t="n">
-        <v>7222905</v>
+        <v>7222859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121066947</v>
+        <v>121066943</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>98102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607445</v>
+        <v>607316</v>
       </c>
       <c r="R9" t="n">
-        <v>7222822</v>
+        <v>7222787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121066937</v>
+        <v>121066950</v>
       </c>
       <c r="B10" t="n">
-        <v>97998</v>
+        <v>97035</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607199</v>
+        <v>607623</v>
       </c>
       <c r="R10" t="n">
-        <v>7222792</v>
+        <v>7222896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121066940</v>
+        <v>121066934</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>77533</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607187</v>
+        <v>607175</v>
       </c>
       <c r="R11" t="n">
-        <v>7222814</v>
+        <v>7222788</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121066943</v>
+        <v>121066947</v>
       </c>
       <c r="B12" t="n">
-        <v>98102</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607316</v>
+        <v>607445</v>
       </c>
       <c r="R12" t="n">
-        <v>7222787</v>
+        <v>7222822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066950</v>
+        <v>121066953</v>
       </c>
       <c r="B13" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607623</v>
+        <v>607733</v>
       </c>
       <c r="R13" t="n">
-        <v>7222896</v>
+        <v>7222910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066944</v>
+        <v>121066941</v>
       </c>
       <c r="B14" t="n">
-        <v>79683</v>
+        <v>79710</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607423</v>
+        <v>607301</v>
       </c>
       <c r="R14" t="n">
-        <v>7222826</v>
+        <v>7222757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121066946</v>
+        <v>121066949</v>
       </c>
       <c r="B15" t="n">
-        <v>78683</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607439</v>
+        <v>607549</v>
       </c>
       <c r="R15" t="n">
-        <v>7222815</v>
+        <v>7222874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066949</v>
+        <v>121066940</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607549</v>
+        <v>607187</v>
       </c>
       <c r="R16" t="n">
-        <v>7222874</v>
+        <v>7222814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121066952</v>
+        <v>121066954</v>
       </c>
       <c r="B17" t="n">
-        <v>82385</v>
+        <v>79710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607715</v>
+        <v>607755</v>
       </c>
       <c r="R17" t="n">
-        <v>7222908</v>
+        <v>7222905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066934</v>
+        <v>121066937</v>
       </c>
       <c r="B18" t="n">
-        <v>77533</v>
+        <v>97998</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607175</v>
+        <v>607199</v>
       </c>
       <c r="R18" t="n">
-        <v>7222788</v>
+        <v>7222792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121066955</v>
+        <v>121066938</v>
       </c>
       <c r="B20" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607758</v>
+        <v>607194</v>
       </c>
       <c r="R20" t="n">
-        <v>7222909</v>
+        <v>7222802</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121066939</v>
+        <v>121066946</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>78683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607185</v>
+        <v>607439</v>
       </c>
       <c r="R21" t="n">
-        <v>7222801</v>
+        <v>7222815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 48338-2021 artfynd.xlsx
+++ b/artfynd/A 48338-2021 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066944</v>
+        <v>121066948</v>
       </c>
       <c r="B7" t="n">
-        <v>79683</v>
+        <v>78683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607423</v>
+        <v>607538</v>
       </c>
       <c r="R7" t="n">
-        <v>7222826</v>
+        <v>7222859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066948</v>
+        <v>121066944</v>
       </c>
       <c r="B8" t="n">
-        <v>78683</v>
+        <v>79683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607538</v>
+        <v>607423</v>
       </c>
       <c r="R8" t="n">
-        <v>7222859</v>
+        <v>7222826</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 48338-2021 artfynd.xlsx
+++ b/artfynd/A 48338-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121066939</v>
+        <v>121066937</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607185</v>
+        <v>607199</v>
       </c>
       <c r="R2" t="n">
-        <v>7222801</v>
+        <v>7222792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121066945</v>
+        <v>121066942</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607423</v>
+        <v>607311</v>
       </c>
       <c r="R3" t="n">
-        <v>7222823</v>
+        <v>7222763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066955</v>
+        <v>121066939</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607758</v>
+        <v>607185</v>
       </c>
       <c r="R4" t="n">
-        <v>7222909</v>
+        <v>7222801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>121066952</v>
       </c>
       <c r="B5" t="n">
-        <v>82385</v>
+        <v>82388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121066951</v>
+        <v>121066955</v>
       </c>
       <c r="B6" t="n">
-        <v>79711</v>
+        <v>82388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607676</v>
+        <v>607758</v>
       </c>
       <c r="R6" t="n">
-        <v>7222895</v>
+        <v>7222909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066948</v>
+        <v>121066953</v>
       </c>
       <c r="B7" t="n">
-        <v>78683</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607538</v>
+        <v>607733</v>
       </c>
       <c r="R7" t="n">
-        <v>7222859</v>
+        <v>7222910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121066944</v>
+        <v>121066949</v>
       </c>
       <c r="B8" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607423</v>
+        <v>607549</v>
       </c>
       <c r="R8" t="n">
-        <v>7222826</v>
+        <v>7222874</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121066943</v>
+        <v>121066950</v>
       </c>
       <c r="B9" t="n">
-        <v>98102</v>
+        <v>97048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607316</v>
+        <v>607623</v>
       </c>
       <c r="R9" t="n">
-        <v>7222787</v>
+        <v>7222896</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121066950</v>
+        <v>121066951</v>
       </c>
       <c r="B10" t="n">
-        <v>97035</v>
+        <v>79714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607623</v>
+        <v>607676</v>
       </c>
       <c r="R10" t="n">
-        <v>7222896</v>
+        <v>7222895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121066934</v>
+        <v>121066948</v>
       </c>
       <c r="B11" t="n">
-        <v>77533</v>
+        <v>78686</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607175</v>
+        <v>607538</v>
       </c>
       <c r="R11" t="n">
-        <v>7222788</v>
+        <v>7222859</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121066947</v>
+        <v>121066938</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607445</v>
+        <v>607194</v>
       </c>
       <c r="R12" t="n">
-        <v>7222822</v>
+        <v>7222802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121066953</v>
+        <v>121066954</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>79713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607733</v>
+        <v>607755</v>
       </c>
       <c r="R13" t="n">
-        <v>7222910</v>
+        <v>7222905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121066941</v>
+        <v>121066944</v>
       </c>
       <c r="B14" t="n">
-        <v>79710</v>
+        <v>79686</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607301</v>
+        <v>607423</v>
       </c>
       <c r="R14" t="n">
-        <v>7222757</v>
+        <v>7222826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121066949</v>
+        <v>121066946</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78686</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607549</v>
+        <v>607439</v>
       </c>
       <c r="R15" t="n">
-        <v>7222874</v>
+        <v>7222815</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066940</v>
+        <v>121066947</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607187</v>
+        <v>607445</v>
       </c>
       <c r="R16" t="n">
-        <v>7222814</v>
+        <v>7222822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121066954</v>
+        <v>121066934</v>
       </c>
       <c r="B17" t="n">
-        <v>79710</v>
+        <v>77536</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607755</v>
+        <v>607175</v>
       </c>
       <c r="R17" t="n">
-        <v>7222905</v>
+        <v>7222788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121066937</v>
+        <v>121066943</v>
       </c>
       <c r="B18" t="n">
-        <v>97998</v>
+        <v>98115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607199</v>
+        <v>607316</v>
       </c>
       <c r="R18" t="n">
-        <v>7222792</v>
+        <v>7222787</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121066942</v>
+        <v>121066940</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607311</v>
+        <v>607187</v>
       </c>
       <c r="R19" t="n">
-        <v>7222763</v>
+        <v>7222814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121066938</v>
+        <v>121066941</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>79713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607194</v>
+        <v>607301</v>
       </c>
       <c r="R20" t="n">
-        <v>7222802</v>
+        <v>7222757</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121066946</v>
+        <v>121066945</v>
       </c>
       <c r="B21" t="n">
-        <v>78683</v>
+        <v>79685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607439</v>
+        <v>607423</v>
       </c>
       <c r="R21" t="n">
-        <v>7222815</v>
+        <v>7222823</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
